--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLIII/LTAIPT_A63F43A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLIII/LTAIPT_A63F43A.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="126">
   <si>
     <t>49014</t>
   </si>
@@ -142,16 +142,109 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>AC26C2BBA9431ECD2983365A1CE24E21</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>2CE3DA712157E336C181559F7F2D8E8E</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
+  </si>
+  <si>
+    <t>Transferencias, Asignaciones, Subsidios y Otras Ayudas</t>
+  </si>
+  <si>
+    <t>Subsidios y Subvenciones</t>
+  </si>
+  <si>
+    <t>7982397</t>
+  </si>
+  <si>
+    <t>Recursos Estatales</t>
+  </si>
+  <si>
+    <t>Secretaría de Planeación y Finanzas del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>30/01/2023</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/1er%20Trimestre/Informacion%20Presupuestal/Informacion%20Presupuestal.pdf</t>
+  </si>
+  <si>
+    <t>Departamento de Programación y Presupuesto</t>
+  </si>
+  <si>
+    <t>25/04/2023</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>8DA5BBBF61015F238644B3D5A900F3FD</t>
+  </si>
+  <si>
+    <t>6548406</t>
+  </si>
+  <si>
+    <t>13/01/2023</t>
+  </si>
+  <si>
+    <t>6CD75D97CE83A774E1186572EEB0C1C5</t>
+  </si>
+  <si>
+    <t>25580668</t>
+  </si>
+  <si>
+    <t>Recursos Federales</t>
+  </si>
+  <si>
+    <t>Subsecretaría de Educación Media Superior</t>
+  </si>
+  <si>
+    <t>31/01/2023</t>
+  </si>
+  <si>
+    <t>89484C1E834F8FA3A43E3856E0AFF939</t>
+  </si>
+  <si>
+    <t>135980</t>
+  </si>
+  <si>
+    <t>14/02/2023</t>
+  </si>
+  <si>
+    <t>DAA82E7B9DE80FC145072EF441584F5D</t>
+  </si>
+  <si>
+    <t>13/02/2023</t>
+  </si>
+  <si>
+    <t>553C359867D389465F719925C4E076F1</t>
+  </si>
+  <si>
+    <t>13118291</t>
+  </si>
+  <si>
+    <t>2B344D09BBF4B3D5939FAEFAF62F3668</t>
+  </si>
+  <si>
+    <t>62427</t>
+  </si>
+  <si>
+    <t>27/01/2023</t>
+  </si>
+  <si>
+    <t>1031065BD5DA8034B653BBE99F36DDE2</t>
+  </si>
+  <si>
+    <t>58515</t>
+  </si>
+  <si>
+    <t>67997C28027AD4577221519990A88B74</t>
   </si>
   <si>
     <t>Ingresos por Venta de Bienes, Prestación de Servicios y Otros Ingresos</t>
@@ -160,290 +253,145 @@
     <t>Ingresos por ventas de bienes y prestación de servicios</t>
   </si>
   <si>
-    <t>51024</t>
+    <t>6553753</t>
   </si>
   <si>
     <t>Ingresos Propios</t>
   </si>
   <si>
-    <t>Secretaría de Planeación y Finanzas del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>15/12/2022</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Depto.%20de%20Programacion%20y%20Presupuesto/4to_Trimestre/Informacion%20Presupuestal/prsupuestal_4to_trimestre.pdf</t>
-  </si>
-  <si>
-    <t>Departamento de Programación y Presupuesto</t>
-  </si>
-  <si>
-    <t>13/01/2023</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>936028F0E7ADD20455E9FD044AF6D10A</t>
-  </si>
-  <si>
-    <t>Transferencias, Asignaciones, Subsidios y Otras Ayudas</t>
-  </si>
-  <si>
-    <t>Subsidios y Subvenciones</t>
-  </si>
-  <si>
-    <t>9758908</t>
-  </si>
-  <si>
-    <t>Recursos Federales</t>
-  </si>
-  <si>
-    <t>Subsecretaría de Educación Media Superior</t>
-  </si>
-  <si>
-    <t>14/12/2022</t>
-  </si>
-  <si>
-    <t>47D2C17C59D2C8E7E599A3A13E02BD2F</t>
+    <t>15/02/2023</t>
+  </si>
+  <si>
+    <t>577992E5DD856A1C5FC45713F41C040D</t>
+  </si>
+  <si>
+    <t>60804.5</t>
+  </si>
+  <si>
+    <t>24/02/2023</t>
+  </si>
+  <si>
+    <t>332E9E4D13D7182E2544D15E4A96446A</t>
+  </si>
+  <si>
+    <t>58516.5</t>
+  </si>
+  <si>
+    <t>B5EF78955F6DA4403499185998C5EFD8</t>
+  </si>
+  <si>
+    <t>25038403.5</t>
+  </si>
+  <si>
+    <t>48CC7FAB945FE95916D53BE0D1C32B16</t>
+  </si>
+  <si>
+    <t>7642987.5</t>
+  </si>
+  <si>
+    <t>4264E6FA240DBCEF8BAB97A49AAF640F</t>
+  </si>
+  <si>
+    <t>13711.05</t>
+  </si>
+  <si>
+    <t>13/03/2023</t>
+  </si>
+  <si>
+    <t>CCC020E6268329F6F95901388410B14E</t>
+  </si>
+  <si>
+    <t>10/03/2023</t>
+  </si>
+  <si>
+    <t>560D512CD70F94FB646E9EEE0C2572A4</t>
+  </si>
+  <si>
+    <t>12763743</t>
+  </si>
+  <si>
+    <t>3AC73C08568B09F155928EEAC65C6B84</t>
+  </si>
+  <si>
+    <t>Aprovechamientos</t>
+  </si>
+  <si>
+    <t>9780</t>
+  </si>
+  <si>
+    <t>Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>28/02/2023</t>
+  </si>
+  <si>
+    <t>08E32BED83F7B6BC26823B1582194903</t>
+  </si>
+  <si>
+    <t>Derechos</t>
+  </si>
+  <si>
+    <t>Derechos por Prestación de Servicios</t>
+  </si>
+  <si>
+    <t>236193</t>
+  </si>
+  <si>
+    <t>AF07DF2162F449BBA30031F996ECA0DB</t>
   </si>
   <si>
     <t>Productos</t>
   </si>
   <si>
-    <t>81526.98</t>
-  </si>
-  <si>
-    <t>Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>30/11/2022</t>
-  </si>
-  <si>
-    <t>894F04C9617B3595A08319D8CF9568C8</t>
-  </si>
-  <si>
-    <t>Derechos</t>
-  </si>
-  <si>
-    <t>Derechos por Prestación de Servicios</t>
-  </si>
-  <si>
-    <t>435422.08</t>
-  </si>
-  <si>
-    <t>B25D6B4EB8040E8DE9C2EA4B25F9AACA</t>
-  </si>
-  <si>
-    <t>38179</t>
-  </si>
-  <si>
-    <t>22/11/2022</t>
-  </si>
-  <si>
-    <t>C508969F1C8754E4C58E7687B5CA1722</t>
-  </si>
-  <si>
-    <t>1652974</t>
-  </si>
-  <si>
-    <t>15/11/2022</t>
-  </si>
-  <si>
-    <t>1508C9A800966561DF37A060986E1C03</t>
-  </si>
-  <si>
-    <t>Aprovechamientos</t>
-  </si>
-  <si>
-    <t>5424750.45</t>
-  </si>
-  <si>
-    <t>B0087A8464D5176AB0A8DED11F81553E</t>
-  </si>
-  <si>
-    <t>109839.05</t>
-  </si>
-  <si>
-    <t>C6C8B584138C98CBC36A9479DA301D07</t>
-  </si>
-  <si>
-    <t>-4268865.57</t>
-  </si>
-  <si>
-    <t>0406F5A0F2E25052BC3B3BD9D8AF9937</t>
-  </si>
-  <si>
-    <t>2114</t>
-  </si>
-  <si>
-    <t>28/12/2022</t>
-  </si>
-  <si>
-    <t>1FC06D303D9EDDD84806F6634E7A86D4</t>
-  </si>
-  <si>
-    <t>9097</t>
-  </si>
-  <si>
-    <t>23/12/2022</t>
-  </si>
-  <si>
-    <t>4F4511486D85CB08AD8569D0ED7C5A7F</t>
-  </si>
-  <si>
-    <t>Participaciones, Aportaciones, Convenios, Incentivos Derivados de la Colaboración Fiscal y
-Fondos Distintos de Aportaciones</t>
-  </si>
-  <si>
-    <t>Aportaciones</t>
-  </si>
-  <si>
-    <t>105662</t>
-  </si>
-  <si>
-    <t>Transferencias Federales Etiquetadas</t>
-  </si>
-  <si>
-    <t>5E967A4D3FE7F647CA739AFF90AF076E</t>
-  </si>
-  <si>
-    <t>195208</t>
-  </si>
-  <si>
-    <t>11/11/2022</t>
-  </si>
-  <si>
-    <t>AF87930424F1B72B0A81F67AD1105C8B</t>
-  </si>
-  <si>
-    <t>49557301</t>
-  </si>
-  <si>
-    <t>69441860B8C20CB0EDA655FFC0634F1E</t>
-  </si>
-  <si>
-    <t>63705.63</t>
-  </si>
-  <si>
-    <t>31/10/2022</t>
-  </si>
-  <si>
-    <t>1F30FB250C71E13B1FC28D00EB4A9DBA</t>
-  </si>
-  <si>
-    <t>670768.69</t>
-  </si>
-  <si>
-    <t>186A5B802822A6E19E8172581C87BB13</t>
-  </si>
-  <si>
-    <t>5D90FAE6A39FB82ABA9F6F1164A323F5</t>
-  </si>
-  <si>
-    <t>166667</t>
-  </si>
-  <si>
-    <t>7063CCA8A31049B0A20FE098F37868AA</t>
-  </si>
-  <si>
-    <t>115498.75</t>
-  </si>
-  <si>
-    <t>Recursos Estatales</t>
-  </si>
-  <si>
-    <t>20/10/2022</t>
-  </si>
-  <si>
-    <t>0A837A3E2071C2D8DC1BEBB3D0DFFD28</t>
-  </si>
-  <si>
-    <t>13019601.02</t>
-  </si>
-  <si>
-    <t>27/10/2022</t>
-  </si>
-  <si>
-    <t>F6772DC72BF4D2423F247397B7037A02</t>
-  </si>
-  <si>
-    <t>9905564.1</t>
-  </si>
-  <si>
-    <t>33BD6AC9048D2C51356F5BE2DC4DF775</t>
-  </si>
-  <si>
-    <t>A2A9C1414FE3193937B4B7CA066753CC</t>
-  </si>
-  <si>
-    <t>125000</t>
-  </si>
-  <si>
-    <t>992AAD35C42870FEFAFA00A093FF0621</t>
-  </si>
-  <si>
-    <t>195207</t>
-  </si>
-  <si>
-    <t>10/10/2022</t>
-  </si>
-  <si>
-    <t>E4BE4267982B6C9DEA62BD07A4BDEB91</t>
-  </si>
-  <si>
-    <t>29987849</t>
-  </si>
-  <si>
-    <t>D466AF28F61A2A2B946D4215BE0B38C5</t>
-  </si>
-  <si>
-    <t>105666</t>
-  </si>
-  <si>
-    <t>09/12/2022</t>
-  </si>
-  <si>
-    <t>51EE9E15A550F20662266169A78B64C3</t>
-  </si>
-  <si>
-    <t>166663</t>
-  </si>
-  <si>
-    <t>CE11CA6C29135B428AC69FA4AE0C77BC</t>
-  </si>
-  <si>
-    <t>227004.75</t>
-  </si>
-  <si>
-    <t>B5C2366F388FA6E11710C183F96F342D</t>
-  </si>
-  <si>
-    <t>16810893.96</t>
-  </si>
-  <si>
-    <t>91421F51A0A471228A066279D0B78110</t>
-  </si>
-  <si>
-    <t>60130</t>
-  </si>
-  <si>
-    <t>DA26D6891F6473B1034A3E37F0D13508</t>
-  </si>
-  <si>
-    <t>4B55383350B7FB1F04F4ED41CAC4C925</t>
-  </si>
-  <si>
-    <t>149562.75</t>
-  </si>
-  <si>
-    <t>C728EA6B6B80D25AFB316EBD4CCDF14D</t>
-  </si>
-  <si>
-    <t>5017869.5</t>
-  </si>
-  <si>
-    <t>22309EBD58F6FA1B12D2F3AA184D97F9</t>
+    <t>839.77</t>
+  </si>
+  <si>
+    <t>4C74BFA3556C1271BD06DDF01AA1740A</t>
+  </si>
+  <si>
+    <t>61872</t>
+  </si>
+  <si>
+    <t>24/03/2023</t>
+  </si>
+  <si>
+    <t>61AB75CE78D62C0BDAD3B23CF6044702</t>
+  </si>
+  <si>
+    <t>58517</t>
+  </si>
+  <si>
+    <t>327F10A65778A6586896AFB140972ACE</t>
+  </si>
+  <si>
+    <t>2899055</t>
+  </si>
+  <si>
+    <t>4A52FFC1D06E1DA165D44EA91735814D</t>
+  </si>
+  <si>
+    <t>047D6EE41B43E75F5BCA605A3A354889</t>
+  </si>
+  <si>
+    <t>1735103</t>
+  </si>
+  <si>
+    <t>7A4AA0EDD831EF51267F5DB98156A34C</t>
+  </si>
+  <si>
+    <t>309098</t>
+  </si>
+  <si>
+    <t>83B79156D2E1BA1C2111ACC1E2B925BE</t>
+  </si>
+  <si>
+    <t>19406.8</t>
+  </si>
+  <si>
+    <t>5E10F948338900A49F069B67646A987C</t>
+  </si>
+  <si>
+    <t>5563961</t>
   </si>
 </sst>
 </file>
@@ -836,20 +784,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="76.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="47.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="58.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="185.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="169" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
@@ -1105,22 +1053,22 @@
         <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>52</v>
@@ -1140,34 +1088,34 @@
     </row>
     <row r="10" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>52</v>
@@ -1187,7 +1135,7 @@
     </row>
     <row r="11" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>43</v>
@@ -1199,22 +1147,22 @@
         <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>52</v>
@@ -1234,7 +1182,7 @@
     </row>
     <row r="12" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>43</v>
@@ -1252,16 +1200,16 @@
         <v>47</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>52</v>
@@ -1281,7 +1229,7 @@
     </row>
     <row r="13" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>43</v>
@@ -1299,16 +1247,16 @@
         <v>47</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>52</v>
@@ -1328,7 +1276,7 @@
     </row>
     <row r="14" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>43</v>
@@ -1340,22 +1288,22 @@
         <v>45</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>52</v>
@@ -1375,7 +1323,7 @@
     </row>
     <row r="15" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>43</v>
@@ -1387,22 +1335,22 @@
         <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>52</v>
@@ -1422,7 +1370,7 @@
     </row>
     <row r="16" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
@@ -1434,22 +1382,22 @@
         <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>52</v>
@@ -1469,7 +1417,7 @@
     </row>
     <row r="17" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>43</v>
@@ -1487,7 +1435,7 @@
         <v>47</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>49</v>
@@ -1496,7 +1444,7 @@
         <v>50</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>52</v>
@@ -1516,7 +1464,7 @@
     </row>
     <row r="18" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>43</v>
@@ -1534,7 +1482,7 @@
         <v>47</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>49</v>
@@ -1543,7 +1491,7 @@
         <v>50</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>52</v>
@@ -1563,7 +1511,7 @@
     </row>
     <row r="19" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>43</v>
@@ -1575,22 +1523,22 @@
         <v>45</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>50</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>52</v>
@@ -1610,7 +1558,7 @@
     </row>
     <row r="20" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>43</v>
@@ -1622,22 +1570,22 @@
         <v>45</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>52</v>
@@ -1657,7 +1605,7 @@
     </row>
     <row r="21" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>43</v>
@@ -1669,22 +1617,22 @@
         <v>45</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>52</v>
@@ -1704,7 +1652,7 @@
     </row>
     <row r="22" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>43</v>
@@ -1716,22 +1664,22 @@
         <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>52</v>
@@ -1751,7 +1699,7 @@
     </row>
     <row r="23" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>43</v>
@@ -1763,22 +1711,22 @@
         <v>45</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>52</v>
@@ -1798,7 +1746,7 @@
     </row>
     <row r="24" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>43</v>
@@ -1810,22 +1758,22 @@
         <v>45</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>52</v>
@@ -1845,7 +1793,7 @@
     </row>
     <row r="25" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>43</v>
@@ -1857,22 +1805,22 @@
         <v>45</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>52</v>
@@ -1892,34 +1840,34 @@
     </row>
     <row r="26" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="H26" s="2" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>52</v>
@@ -1939,7 +1887,7 @@
     </row>
     <row r="27" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>43</v>
@@ -1951,22 +1899,22 @@
         <v>45</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>50</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>52</v>
@@ -1986,7 +1934,7 @@
     </row>
     <row r="28" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>43</v>
@@ -1998,22 +1946,22 @@
         <v>45</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>50</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>52</v>
@@ -2033,7 +1981,7 @@
     </row>
     <row r="29" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>43</v>
@@ -2045,16 +1993,16 @@
         <v>45</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>50</v>
@@ -2080,7 +2028,7 @@
     </row>
     <row r="30" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>43</v>
@@ -2092,22 +2040,22 @@
         <v>45</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>52</v>
@@ -2127,7 +2075,7 @@
     </row>
     <row r="31" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>43</v>
@@ -2139,22 +2087,22 @@
         <v>45</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>52</v>
@@ -2174,7 +2122,7 @@
     </row>
     <row r="32" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>43</v>
@@ -2186,22 +2134,22 @@
         <v>45</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>52</v>
@@ -2221,7 +2169,7 @@
     </row>
     <row r="33" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>43</v>
@@ -2233,22 +2181,22 @@
         <v>45</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>52</v>
@@ -2268,7 +2216,7 @@
     </row>
     <row r="34" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>43</v>
@@ -2280,22 +2228,22 @@
         <v>45</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>50</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>52</v>
@@ -2310,335 +2258,6 @@
         <v>54</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O41" s="2" t="s">
         <v>55</v>
       </c>
     </row>
